--- a/output/casestudy_20260831.xlsx
+++ b/output/casestudy_20260831.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>22.1036837999709</v>
+        <v>21.91714789997786</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>22.43621740001254</v>
+        <v>21.82193350000307</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>13.14407390006818</v>
+        <v>12.95056649995968</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>24.54438770003617</v>
+        <v>22.66096640005708</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>25.03927899990231</v>
+        <v>24.45802609995008</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>15.90852420008741</v>
+        <v>15.62055350001901</v>
       </c>
     </row>
   </sheetData>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22.1 초</t>
+          <t>21.9 초</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>22.4 초</t>
+          <t>21.8 초</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13.1 초</t>
+          <t>13.0 초</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.5 초</t>
+          <t>22.7 초</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25.0 초</t>
+          <t>24.5 초</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15.9 초</t>
+          <t>15.6 초</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>125.5 초</t>
+          <t>121.4 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260831.xlsx
+++ b/output/casestudy_20260831.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>21.91714789997786</v>
+        <v>20.71430850005709</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>21.82193350000307</v>
+        <v>20.77884109993465</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>12.95056649995968</v>
+        <v>12.31468229996972</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>22.66096640005708</v>
+        <v>21.55344229983166</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>24.45802609995008</v>
+        <v>23.34059439995326</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>15.62055350001901</v>
+        <v>14.76062139985152</v>
       </c>
     </row>
   </sheetData>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21.9 초</t>
+          <t>20.7 초</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21.8 초</t>
+          <t>20.8 초</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13.0 초</t>
+          <t>12.3 초</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.7 초</t>
+          <t>21.6 초</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24.5 초</t>
+          <t>23.3 초</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15.6 초</t>
+          <t>14.8 초</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>121.4 초</t>
+          <t>115.4 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260831.xlsx
+++ b/output/casestudy_20260831.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>20.71430850005709</v>
+        <v>20.26671990007162</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>20.77884109993465</v>
+        <v>20.96156399999745</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>12.31468229996972</v>
+        <v>12.5467956000939</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>21.55344229983166</v>
+        <v>22.07261949987151</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>23.34059439995326</v>
+        <v>23.7679394998122</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>14.76062139985152</v>
+        <v>15.18044420005754</v>
       </c>
     </row>
   </sheetData>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20.7 초</t>
+          <t>20.3 초</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20.8 초</t>
+          <t>21.0 초</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12.3 초</t>
+          <t>12.5 초</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.6 초</t>
+          <t>22.1 초</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>23.3 초</t>
+          <t>23.8 초</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14.8 초</t>
+          <t>15.2 초</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>115.4 초</t>
+          <t>116.9 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260831.xlsx
+++ b/output/casestudy_20260831.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>20.26671990007162</v>
+        <v>21.02365019987337</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>20.96156399999745</v>
+        <v>21.75904670008458</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>12.5467956000939</v>
+        <v>12.85578940017149</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>22.07261949987151</v>
+        <v>22.32401009998284</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>23.7679394998122</v>
+        <v>24.01948540005833</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>15.18044420005754</v>
+        <v>15.3818167001009</v>
       </c>
     </row>
   </sheetData>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20.3 초</t>
+          <t>21.0 초</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21.0 초</t>
+          <t>21.8 초</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12.5 초</t>
+          <t>12.9 초</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.1 초</t>
+          <t>22.3 초</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>23.8 초</t>
+          <t>24.0 초</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15.2 초</t>
+          <t>15.4 초</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>116.9 초</t>
+          <t>119.3 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260831.xlsx
+++ b/output/casestudy_20260831.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>21.02365019987337</v>
+        <v>19.238978699781</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>21.75904670008458</v>
+        <v>19.47019110014662</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>12.85578940017149</v>
+        <v>11.55164680001326</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>22.32401009998284</v>
+        <v>20.24423959990963</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>24.01948540005833</v>
+        <v>21.91878810012713</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>15.3818167001009</v>
+        <v>14.10721050016582</v>
       </c>
     </row>
   </sheetData>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21.0 초</t>
+          <t>19.2 초</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21.8 초</t>
+          <t>19.5 초</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12.9 초</t>
+          <t>11.6 초</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.3 초</t>
+          <t>20.2 초</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24.0 초</t>
+          <t>21.9 초</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15.4 초</t>
+          <t>14.1 초</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>119.3 초</t>
+          <t>108.3 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260831.xlsx
+++ b/output/casestudy_20260831.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>19.238978699781</v>
+        <v>22.75400249985978</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>19.47019110014662</v>
+        <v>20.87279339996167</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>11.55164680001326</v>
+        <v>11.97678699996322</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>20.24423959990963</v>
+        <v>21.96373189985752</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>21.91878810012713</v>
+        <v>22.68827990000136</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>14.10721050016582</v>
+        <v>14.22356219985522</v>
       </c>
     </row>
   </sheetData>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19.2 초</t>
+          <t>22.8 초</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19.5 초</t>
+          <t>20.9 초</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11.6 초</t>
+          <t>12.0 초</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.2 초</t>
+          <t>22.0 초</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21.9 초</t>
+          <t>22.7 초</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14.1 초</t>
+          <t>14.2 초</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>108.3 초</t>
+          <t>116.8 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260831.xlsx
+++ b/output/casestudy_20260831.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>22.75400249985978</v>
+        <v>21.47921400004998</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>20.87279339996167</v>
+        <v>19.77241039997898</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>11.97678699996322</v>
+        <v>11.63750150008127</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>21.96373189985752</v>
+        <v>20.42397379991598</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>22.68827990000136</v>
+        <v>22.05846669990569</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>14.22356219985522</v>
+        <v>14.00924449996091</v>
       </c>
     </row>
   </sheetData>
@@ -1787,13 +1787,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>91585140.33269072</v>
+        <v>91089226.44079876</v>
       </c>
       <c r="E4" t="n">
-        <v>89491355.80484247</v>
+        <v>88989374.69005966</v>
       </c>
       <c r="F4" t="n">
-        <v>91585140.33269072</v>
+        <v>91089226.44079876</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.286161838309573</v>
+        <v>2.30526905627401</v>
       </c>
     </row>
     <row r="5">
@@ -1816,13 +1816,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>91585140.33269072</v>
+        <v>91089226.44079876</v>
       </c>
       <c r="E5" t="n">
-        <v>89491355.80484247</v>
+        <v>88989374.69005966</v>
       </c>
       <c r="F5" t="n">
-        <v>91585140.33269072</v>
+        <v>91089226.44079876</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.286161838309573</v>
+        <v>2.30526905627401</v>
       </c>
     </row>
     <row r="6">
@@ -1985,13 +1985,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>175726343.9721413</v>
+        <v>174695374.9795818</v>
       </c>
       <c r="E11" t="n">
-        <v>171533404.4096842</v>
+        <v>170484995.4955649</v>
       </c>
       <c r="F11" t="n">
-        <v>177538571.5771565</v>
+        <v>176526740.9757071</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.382457746576256</v>
+        <v>3.422566715245459</v>
       </c>
     </row>
     <row r="12">
@@ -2014,13 +2014,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>175726343.9721413</v>
+        <v>174695374.9795818</v>
       </c>
       <c r="E12" t="n">
-        <v>171533404.4096842</v>
+        <v>170484995.4955649</v>
       </c>
       <c r="F12" t="n">
-        <v>177538571.5771565</v>
+        <v>176526740.9757071</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3.382457746576256</v>
+        <v>3.422566715245459</v>
       </c>
     </row>
     <row r="13">
@@ -2183,13 +2183,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>337390034.7585793</v>
+        <v>335115969.2951603</v>
       </c>
       <c r="E18" t="n">
-        <v>330325521.4670224</v>
+        <v>327998630.7924576</v>
       </c>
       <c r="F18" t="n">
-        <v>341098645.5543122</v>
+        <v>338880327.16399</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.158360265483504</v>
+        <v>3.211073496829635</v>
       </c>
     </row>
     <row r="19">
@@ -2212,13 +2212,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>337390034.7585793</v>
+        <v>335115969.2951603</v>
       </c>
       <c r="E19" t="n">
-        <v>330325521.4670224</v>
+        <v>327998630.7924576</v>
       </c>
       <c r="F19" t="n">
-        <v>341098645.5543122</v>
+        <v>338880327.16399</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.158360265483504</v>
+        <v>3.211073496829635</v>
       </c>
     </row>
     <row r="20">
@@ -2386,13 +2386,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>79827677.11935902</v>
+        <v>79319852.16566801</v>
       </c>
       <c r="E25" t="n">
-        <v>79536990.89273691</v>
+        <v>79025103.52082205</v>
       </c>
       <c r="F25" t="n">
-        <v>79827677.11935902</v>
+        <v>79319852.16566801</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.364142158599289</v>
+        <v>0.3715950506694697</v>
       </c>
     </row>
     <row r="26">
@@ -2415,13 +2415,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>79827677.11935902</v>
+        <v>79319852.16566801</v>
       </c>
       <c r="E26" t="n">
-        <v>79536990.89273691</v>
+        <v>79025103.52082205</v>
       </c>
       <c r="F26" t="n">
-        <v>79827677.11935902</v>
+        <v>79319852.16566801</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.364142158599289</v>
+        <v>0.3715950506694697</v>
       </c>
     </row>
     <row r="27">
@@ -2584,13 +2584,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>158405072.2227192</v>
+        <v>157336682.9712462</v>
       </c>
       <c r="E32" t="n">
-        <v>157823699.769475</v>
+        <v>156746326.7116151</v>
       </c>
       <c r="F32" t="n">
-        <v>158405072.2227192</v>
+        <v>157336682.9712462</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.3670163114643157</v>
+        <v>0.3752184477786699</v>
       </c>
     </row>
     <row r="33">
@@ -2613,13 +2613,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>158405072.2227192</v>
+        <v>157336682.9712462</v>
       </c>
       <c r="E33" t="n">
-        <v>157823699.769475</v>
+        <v>156746326.7116151</v>
       </c>
       <c r="F33" t="n">
-        <v>158405072.2227192</v>
+        <v>157336682.9712462</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.3670163114643157</v>
+        <v>0.3752184477786699</v>
       </c>
     </row>
     <row r="34">
@@ -2782,13 +2782,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>315549695.5542245</v>
+        <v>313172441.4176869</v>
       </c>
       <c r="E39" t="n">
-        <v>314353059.6187263</v>
+        <v>311954117.7694283</v>
       </c>
       <c r="F39" t="n">
-        <v>315549695.5542245</v>
+        <v>313175233.8550706</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2797,11 +2797,11 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>기준</t>
+          <t>평탄형</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.3792226556886683</v>
+        <v>0.3899146399959068</v>
       </c>
     </row>
     <row r="40">
@@ -2811,13 +2811,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>315549695.5542245</v>
+        <v>313172441.4176869</v>
       </c>
       <c r="E40" t="n">
-        <v>314353059.6187263</v>
+        <v>311954117.7694283</v>
       </c>
       <c r="F40" t="n">
-        <v>315549695.5542245</v>
+        <v>313175233.8550706</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2826,11 +2826,11 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>기준</t>
+          <t>평탄형</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.3792226556886683</v>
+        <v>0.3899146399959068</v>
       </c>
     </row>
     <row r="41">
@@ -2985,13 +2985,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>83143248.78964472</v>
+        <v>82808665.0878582</v>
       </c>
       <c r="E46" t="n">
-        <v>81458843.4197073</v>
+        <v>81119710.90947247</v>
       </c>
       <c r="F46" t="n">
-        <v>84075473.51490021</v>
+        <v>83746710.66527748</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.112239498394474</v>
+        <v>3.136839327701745</v>
       </c>
     </row>
     <row r="47">
@@ -3014,13 +3014,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>83143248.78964472</v>
+        <v>82808665.0878582</v>
       </c>
       <c r="E47" t="n">
-        <v>81458843.4197073</v>
+        <v>81119710.90947247</v>
       </c>
       <c r="F47" t="n">
-        <v>84075473.51490021</v>
+        <v>83746710.66527748</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.112239498394474</v>
+        <v>3.136839327701745</v>
       </c>
     </row>
     <row r="48">
@@ -3183,13 +3183,13 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>163681184.2055364</v>
+        <v>162976496.4152608</v>
       </c>
       <c r="E53" t="n">
-        <v>160431501.6983366</v>
+        <v>159713326.8771558</v>
       </c>
       <c r="F53" t="n">
-        <v>165441931.9946308</v>
+        <v>164752351.2384591</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.028512926491223</v>
+        <v>3.058544733003507</v>
       </c>
     </row>
     <row r="54">
@@ -3212,13 +3212,13 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>163681184.2055364</v>
+        <v>162976496.4152608</v>
       </c>
       <c r="E54" t="n">
-        <v>160431501.6983366</v>
+        <v>159713326.8771558</v>
       </c>
       <c r="F54" t="n">
-        <v>165441931.9946308</v>
+        <v>164752351.2384591</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.028512926491223</v>
+        <v>3.058544733003507</v>
       </c>
     </row>
     <row r="55">
@@ -3381,13 +3381,13 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>324086295.0804329</v>
+        <v>322508060.0090222</v>
       </c>
       <c r="E60" t="n">
-        <v>317952983.8594131</v>
+        <v>316328145.3441987</v>
       </c>
       <c r="F60" t="n">
-        <v>325269049.2752204</v>
+        <v>323724212.857944</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.249235035460412</v>
+        <v>2.28468159624218</v>
       </c>
     </row>
     <row r="61">
@@ -3410,13 +3410,13 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>324086295.0804329</v>
+        <v>322508060.0090222</v>
       </c>
       <c r="E61" t="n">
-        <v>317952983.8594131</v>
+        <v>316328145.3441987</v>
       </c>
       <c r="F61" t="n">
-        <v>325269049.2752204</v>
+        <v>323724212.857944</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.249235035460412</v>
+        <v>2.28468159624218</v>
       </c>
     </row>
     <row r="62">
@@ -3584,13 +3584,13 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>101789520.7326679</v>
+        <v>101329735.4428229</v>
       </c>
       <c r="E67" t="n">
-        <v>99632504.27401972</v>
+        <v>99167106.6073904</v>
       </c>
       <c r="F67" t="n">
-        <v>101800806.7845564</v>
+        <v>101347227.0178547</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.129946293181648</v>
+        <v>2.151139675563306</v>
       </c>
     </row>
     <row r="68">
@@ -3613,13 +3613,13 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>101789520.7326679</v>
+        <v>101329735.4428229</v>
       </c>
       <c r="E68" t="n">
-        <v>99632504.27401972</v>
+        <v>99167106.6073904</v>
       </c>
       <c r="F68" t="n">
-        <v>101800806.7845564</v>
+        <v>101347227.0178547</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.129946293181648</v>
+        <v>2.151139675563306</v>
       </c>
     </row>
     <row r="69">
@@ -3782,13 +3782,13 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>196135104.7720952</v>
+        <v>195182776.5672636</v>
       </c>
       <c r="E74" t="n">
-        <v>191815701.3480396</v>
+        <v>190847320.5621276</v>
       </c>
       <c r="F74" t="n">
-        <v>198141301.5120668</v>
+        <v>197206558.5548496</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.192469271047957</v>
+        <v>3.224658469435905</v>
       </c>
     </row>
     <row r="75">
@@ -3811,13 +3811,13 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>196135104.7720952</v>
+        <v>195182776.5672636</v>
       </c>
       <c r="E75" t="n">
-        <v>191815701.3480396</v>
+        <v>190847320.5621276</v>
       </c>
       <c r="F75" t="n">
-        <v>198141301.5120668</v>
+        <v>197206558.5548496</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.192469271047957</v>
+        <v>3.224658469435905</v>
       </c>
     </row>
     <row r="76">
@@ -3980,13 +3980,13 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>378207556.3584881</v>
+        <v>376124065.2845831</v>
       </c>
       <c r="E81" t="n">
-        <v>370902119.6483784</v>
+        <v>368770372.4855566</v>
       </c>
       <c r="F81" t="n">
-        <v>382304105.4241347</v>
+        <v>380271226.7654672</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.982438748102587</v>
+        <v>3.024381933320381</v>
       </c>
     </row>
     <row r="82">
@@ -4009,13 +4009,13 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>378207556.3584881</v>
+        <v>376124065.2845831</v>
       </c>
       <c r="E82" t="n">
-        <v>370902119.6483784</v>
+        <v>368770372.4855566</v>
       </c>
       <c r="F82" t="n">
-        <v>382304105.4241347</v>
+        <v>380271226.7654672</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.982438748102587</v>
+        <v>3.024381933320381</v>
       </c>
     </row>
     <row r="83">
@@ -4183,13 +4183,13 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>83446152.48947334</v>
+        <v>82923499.78135967</v>
       </c>
       <c r="E88" t="n">
-        <v>81962507.35134506</v>
+        <v>81434169.65732384</v>
       </c>
       <c r="F88" t="n">
-        <v>83910302.96401405</v>
+        <v>83395395.81188011</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.321283017538772</v>
+        <v>2.351719942645667</v>
       </c>
     </row>
     <row r="89">
@@ -4212,13 +4212,13 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>83446152.48947334</v>
+        <v>82923499.78135967</v>
       </c>
       <c r="E89" t="n">
-        <v>81962507.35134506</v>
+        <v>81434169.65732384</v>
       </c>
       <c r="F89" t="n">
-        <v>83910302.96401405</v>
+        <v>83395395.81188011</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.321283017538772</v>
+        <v>2.351719942645667</v>
       </c>
     </row>
     <row r="90">
@@ -4381,13 +4381,13 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>164238950.2571878</v>
+        <v>163140686.1178045</v>
       </c>
       <c r="E95" t="n">
-        <v>161752897.5920959</v>
+        <v>160640355.0297017</v>
       </c>
       <c r="F95" t="n">
-        <v>165110598.8201962</v>
+        <v>164030467.5356884</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.033607322663038</v>
+        <v>2.066757814519487</v>
       </c>
     </row>
     <row r="96">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>164238950.2571878</v>
+        <v>163140686.1178045</v>
       </c>
       <c r="E96" t="n">
-        <v>161752897.5920959</v>
+        <v>160640355.0297017</v>
       </c>
       <c r="F96" t="n">
-        <v>165110598.8201962</v>
+        <v>164030467.5356884</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.033607322663038</v>
+        <v>2.066757814519487</v>
       </c>
     </row>
     <row r="97">
@@ -4579,13 +4579,13 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>325181176.5735693</v>
+        <v>322738037.6217999</v>
       </c>
       <c r="E102" t="n">
-        <v>320636989.5653667</v>
+        <v>318151702.8485751</v>
       </c>
       <c r="F102" t="n">
-        <v>326965069.5956106</v>
+        <v>324571420.9923706</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.935399410729233</v>
+        <v>1.977906164432879</v>
       </c>
     </row>
     <row r="103">
@@ -4608,13 +4608,13 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>325181176.5735693</v>
+        <v>322738037.6217999</v>
       </c>
       <c r="E103" t="n">
-        <v>320636989.5653667</v>
+        <v>318151702.8485751</v>
       </c>
       <c r="F103" t="n">
-        <v>326965069.5956106</v>
+        <v>324571420.9923706</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.935399410729233</v>
+        <v>1.977906164432879</v>
       </c>
     </row>
     <row r="104">
@@ -4782,13 +4782,13 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>88082225.51290274</v>
+        <v>87554246.91252422</v>
       </c>
       <c r="E109" t="n">
-        <v>86218028.26469135</v>
+        <v>85681918.82675982</v>
       </c>
       <c r="F109" t="n">
-        <v>89007363.41221714</v>
+        <v>88489082.37075377</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.133825158495734</v>
+        <v>3.17232755588133</v>
       </c>
     </row>
     <row r="110">
@@ -4811,13 +4811,13 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>88082225.51290274</v>
+        <v>87554246.91252422</v>
       </c>
       <c r="E110" t="n">
-        <v>86218028.26469135</v>
+        <v>85681918.82675982</v>
       </c>
       <c r="F110" t="n">
-        <v>89007363.41221714</v>
+        <v>88489082.37075377</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.133825158495734</v>
+        <v>3.17232755588133</v>
       </c>
     </row>
     <row r="111">
@@ -4980,13 +4980,13 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>168995761.0519023</v>
+        <v>167835324.5902858</v>
       </c>
       <c r="E116" t="n">
-        <v>165289434.3347812</v>
+        <v>164102472.5923471</v>
       </c>
       <c r="F116" t="n">
-        <v>170839932.9884553</v>
+        <v>169707067.1231384</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.248946868908692</v>
+        <v>3.302510983072156</v>
       </c>
     </row>
     <row r="117">
@@ -5009,13 +5009,13 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>168995761.0519023</v>
+        <v>167835324.5902858</v>
       </c>
       <c r="E117" t="n">
-        <v>165289434.3347812</v>
+        <v>164102472.5923471</v>
       </c>
       <c r="F117" t="n">
-        <v>170839932.9884553</v>
+        <v>169707067.1231384</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.248946868908692</v>
+        <v>3.302510983072156</v>
       </c>
     </row>
     <row r="118">
@@ -5178,13 +5178,13 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>323124717.5811791</v>
+        <v>320373660.1922641</v>
       </c>
       <c r="E123" t="n">
-        <v>314432729.4898615</v>
+        <v>311615159.9630437</v>
       </c>
       <c r="F123" t="n">
-        <v>328233188.4269361</v>
+        <v>325559171.9981222</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>4.204467867254261</v>
+        <v>4.28309604963578</v>
       </c>
     </row>
     <row r="124">
@@ -5207,13 +5207,13 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>323124717.5811791</v>
+        <v>320373660.1922641</v>
       </c>
       <c r="E124" t="n">
-        <v>314432729.4898615</v>
+        <v>311615159.9630437</v>
       </c>
       <c r="F124" t="n">
-        <v>328233188.4269361</v>
+        <v>325559171.9981222</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>4.204467867254261</v>
+        <v>4.28309604963578</v>
       </c>
     </row>
     <row r="125">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22.8 초</t>
+          <t>21.5 초</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20.9 초</t>
+          <t>19.8 초</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12.0 초</t>
+          <t>11.6 초</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.0 초</t>
+          <t>20.4 초</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22.7 초</t>
+          <t>22.1 초</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14.2 초</t>
+          <t>14.0 초</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>116.8 초</t>
+          <t>111.4 초</t>
         </is>
       </c>
     </row>
